--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127727459</v>
       </c>
       <c r="B2" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>127727480</v>
       </c>
       <c r="B3" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>127727425</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>127727463</v>
       </c>
       <c r="B5" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>127727467</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>127727430</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727431</v>
+        <v>127727458</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,39 +1403,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545054</v>
+        <v>545033</v>
       </c>
       <c r="R8" t="n">
-        <v>7244432</v>
+        <v>7244298</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1470,11 +1465,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1496,12 +1486,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1519,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727458</v>
+        <v>127727431</v>
       </c>
       <c r="B9" t="n">
-        <v>91348</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,34 +1520,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545033</v>
+        <v>545054</v>
       </c>
       <c r="R9" t="n">
-        <v>7244298</v>
+        <v>7244432</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1592,6 +1587,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
         <v>127727454</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>127727437</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>127727427</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>127727469</v>
       </c>
       <c r="B13" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127727464</v>
       </c>
       <c r="B14" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>127727443</v>
       </c>
       <c r="B15" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>127727423</v>
       </c>
       <c r="B16" t="n">
-        <v>92027</v>
+        <v>92029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>127727451</v>
       </c>
       <c r="B17" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2582,50 +2582,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727426</v>
+        <v>127727442</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>91786</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545100</v>
+        <v>545031</v>
       </c>
       <c r="R18" t="n">
-        <v>7244443</v>
+        <v>7244445</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2660,11 +2655,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2684,9 +2674,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2707,7 +2702,7 @@
         <v>127727474</v>
       </c>
       <c r="B19" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,32 +2816,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127727442</v>
+        <v>127727466</v>
       </c>
       <c r="B20" t="n">
-        <v>91784</v>
+        <v>91350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2856,10 +2851,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545031</v>
+        <v>545041</v>
       </c>
       <c r="R20" t="n">
-        <v>7244445</v>
+        <v>7244311</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2915,12 +2910,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2938,10 +2933,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727466</v>
+        <v>127727426</v>
       </c>
       <c r="B21" t="n">
-        <v>91348</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2949,34 +2944,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545041</v>
+        <v>545100</v>
       </c>
       <c r="R21" t="n">
-        <v>7244311</v>
+        <v>7244443</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3011,6 +3011,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3030,14 +3035,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3058,7 +3058,7 @@
         <v>127727433</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,32 +3177,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727472</v>
+        <v>127727421</v>
       </c>
       <c r="B23" t="n">
-        <v>91348</v>
+        <v>92029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544968</v>
+        <v>544863</v>
       </c>
       <c r="R23" t="n">
-        <v>7244261</v>
+        <v>7244369</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3271,12 +3271,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727421</v>
+        <v>127727472</v>
       </c>
       <c r="B24" t="n">
-        <v>92027</v>
+        <v>91350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544863</v>
+        <v>544968</v>
       </c>
       <c r="R24" t="n">
-        <v>7244369</v>
+        <v>7244261</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727458</v>
+        <v>127727431</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,34 +1403,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545033</v>
+        <v>545054</v>
       </c>
       <c r="R8" t="n">
-        <v>7244298</v>
+        <v>7244432</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,6 +1470,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1486,12 +1496,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1509,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727431</v>
+        <v>127727458</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,39 +1530,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545054</v>
+        <v>545033</v>
       </c>
       <c r="R9" t="n">
-        <v>7244432</v>
+        <v>7244298</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1587,11 +1592,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727474</v>
+        <v>127727426</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,34 +2710,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544931</v>
+        <v>545100</v>
       </c>
       <c r="R19" t="n">
-        <v>7244255</v>
+        <v>7244443</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2772,6 +2777,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2791,14 +2801,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2933,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727426</v>
+        <v>127727474</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2944,39 +2949,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545100</v>
+        <v>544931</v>
       </c>
       <c r="R21" t="n">
-        <v>7244443</v>
+        <v>7244255</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3011,11 +3011,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3035,9 +3030,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3055,50 +3055,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727433</v>
+        <v>127727421</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>92029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545069</v>
+        <v>544863</v>
       </c>
       <c r="R22" t="n">
-        <v>7244335</v>
+        <v>7244369</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3133,11 +3128,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3157,9 +3147,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3177,32 +3172,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727421</v>
+        <v>127727472</v>
       </c>
       <c r="B23" t="n">
-        <v>92029</v>
+        <v>91350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3212,10 +3207,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544863</v>
+        <v>544968</v>
       </c>
       <c r="R23" t="n">
-        <v>7244369</v>
+        <v>7244261</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3271,12 +3266,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3294,10 +3289,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727472</v>
+        <v>127727433</v>
       </c>
       <c r="B24" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3305,34 +3300,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544968</v>
+        <v>545069</v>
       </c>
       <c r="R24" t="n">
-        <v>7244261</v>
+        <v>7244335</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3367,6 +3367,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3386,14 +3391,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -2465,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727451</v>
+        <v>127727426</v>
       </c>
       <c r="B17" t="n">
-        <v>91328</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,34 +2476,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545094</v>
+        <v>545100</v>
       </c>
       <c r="R17" t="n">
-        <v>7244392</v>
+        <v>7244443</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2538,6 +2543,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2557,14 +2567,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2582,32 +2587,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727442</v>
+        <v>127727451</v>
       </c>
       <c r="B18" t="n">
-        <v>91786</v>
+        <v>91328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2617,10 +2622,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545031</v>
+        <v>545094</v>
       </c>
       <c r="R18" t="n">
-        <v>7244445</v>
+        <v>7244392</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2676,12 +2681,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2699,50 +2704,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727426</v>
+        <v>127727442</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>91786</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545100</v>
+        <v>545031</v>
       </c>
       <c r="R19" t="n">
-        <v>7244443</v>
+        <v>7244445</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2777,11 +2777,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2801,9 +2796,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727463</v>
+        <v>127727430</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545110</v>
+        <v>544978</v>
       </c>
       <c r="R5" t="n">
-        <v>7244381</v>
+        <v>7244472</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,6 +1109,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,12 +1135,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt 2-stammig</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,7 +1158,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727467</v>
+        <v>127727463</v>
       </c>
       <c r="B6" t="n">
         <v>91350</v>
@@ -1183,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544936</v>
+        <v>545110</v>
       </c>
       <c r="R6" t="n">
-        <v>7244266</v>
+        <v>7244381</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,12 +1252,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Levande, grov gran</t>
+          <t>Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Levande, grov gran</t>
+          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727430</v>
+        <v>127727467</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544978</v>
+        <v>544936</v>
       </c>
       <c r="R7" t="n">
-        <v>7244472</v>
+        <v>7244266</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,11 +1348,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Levande, grov gran</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Levande, grov gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727431</v>
+        <v>127727458</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,39 +1403,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545054</v>
+        <v>545033</v>
       </c>
       <c r="R8" t="n">
-        <v>7244432</v>
+        <v>7244298</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1470,11 +1465,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1496,12 +1486,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1519,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727458</v>
+        <v>127727431</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,34 +1520,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545033</v>
+        <v>545054</v>
       </c>
       <c r="R9" t="n">
-        <v>7244298</v>
+        <v>7244432</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1592,6 +1587,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727437</v>
+        <v>127727427</v>
       </c>
       <c r="B11" t="n">
         <v>57663</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545110</v>
+        <v>544900</v>
       </c>
       <c r="R11" t="n">
-        <v>7244346</v>
+        <v>7244331</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack lågt ned</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,14 +1850,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granlåga, ny rotvälta</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, ny rotvälta</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1875,7 +1870,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727427</v>
+        <v>127727437</v>
       </c>
       <c r="B12" t="n">
         <v>57663</v>
@@ -1915,10 +1910,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544900</v>
+        <v>545110</v>
       </c>
       <c r="R12" t="n">
-        <v>7244331</v>
+        <v>7244346</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1955,7 +1950,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack lågt ned</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,9 +1972,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granlåga, ny rotvälta</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, ny rotvälta</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727426</v>
+        <v>127727451</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>91328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,39 +2476,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545100</v>
+        <v>545094</v>
       </c>
       <c r="R17" t="n">
-        <v>7244443</v>
+        <v>7244392</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2543,11 +2538,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2567,9 +2557,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2587,32 +2582,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727451</v>
+        <v>127727442</v>
       </c>
       <c r="B18" t="n">
-        <v>91328</v>
+        <v>91786</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2622,10 +2617,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545094</v>
+        <v>545031</v>
       </c>
       <c r="R18" t="n">
-        <v>7244392</v>
+        <v>7244445</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2681,12 +2676,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2704,32 +2699,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727442</v>
+        <v>127727474</v>
       </c>
       <c r="B19" t="n">
-        <v>91786</v>
+        <v>91350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,10 +2734,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545031</v>
+        <v>544931</v>
       </c>
       <c r="R19" t="n">
-        <v>7244445</v>
+        <v>7244255</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2798,12 +2793,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2938,10 +2933,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727474</v>
+        <v>127727426</v>
       </c>
       <c r="B21" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2949,34 +2944,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544931</v>
+        <v>545100</v>
       </c>
       <c r="R21" t="n">
-        <v>7244255</v>
+        <v>7244443</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3011,6 +3011,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3030,14 +3035,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127727459</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>127727480</v>
       </c>
       <c r="B3" t="n">
-        <v>88735</v>
+        <v>88741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>127727463</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>127727467</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727458</v>
+        <v>127727431</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,34 +1403,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545033</v>
+        <v>545054</v>
       </c>
       <c r="R8" t="n">
-        <v>7244298</v>
+        <v>7244432</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,6 +1470,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1486,12 +1496,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1509,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727431</v>
+        <v>127727458</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>91356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,39 +1530,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545054</v>
+        <v>545033</v>
       </c>
       <c r="R9" t="n">
-        <v>7244432</v>
+        <v>7244298</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1587,11 +1592,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
         <v>127727454</v>
       </c>
       <c r="B10" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727427</v>
+        <v>127727437</v>
       </c>
       <c r="B11" t="n">
         <v>57663</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544900</v>
+        <v>545110</v>
       </c>
       <c r="R11" t="n">
-        <v>7244331</v>
+        <v>7244346</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack lågt ned</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,9 +1850,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granlåga, ny rotvälta</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, ny rotvälta</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1870,7 +1875,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727437</v>
+        <v>127727427</v>
       </c>
       <c r="B12" t="n">
         <v>57663</v>
@@ -1910,10 +1915,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545110</v>
+        <v>544900</v>
       </c>
       <c r="R12" t="n">
-        <v>7244346</v>
+        <v>7244331</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1950,7 +1955,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack lågt ned</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,14 +1977,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granlåga, ny rotvälta</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, ny rotvälta</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>127727469</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127727464</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>127727443</v>
       </c>
       <c r="B15" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>127727423</v>
       </c>
       <c r="B16" t="n">
-        <v>92029</v>
+        <v>92035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2465,32 +2465,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727451</v>
+        <v>127727442</v>
       </c>
       <c r="B17" t="n">
-        <v>91328</v>
+        <v>91792</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545094</v>
+        <v>545031</v>
       </c>
       <c r="R17" t="n">
-        <v>7244392</v>
+        <v>7244445</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2582,45 +2582,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727442</v>
+        <v>127727426</v>
       </c>
       <c r="B18" t="n">
-        <v>91786</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545031</v>
+        <v>545100</v>
       </c>
       <c r="R18" t="n">
-        <v>7244445</v>
+        <v>7244443</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2655,6 +2660,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2674,14 +2684,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2699,10 +2704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727474</v>
+        <v>127727451</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>91334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,21 +2715,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2734,10 +2739,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544931</v>
+        <v>545094</v>
       </c>
       <c r="R19" t="n">
-        <v>7244255</v>
+        <v>7244392</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2793,12 +2798,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2816,10 +2821,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127727466</v>
+        <v>127727474</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,10 +2856,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545041</v>
+        <v>544931</v>
       </c>
       <c r="R20" t="n">
-        <v>7244311</v>
+        <v>7244255</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2910,12 +2915,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2933,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727426</v>
+        <v>127727466</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>91356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2944,39 +2949,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545100</v>
+        <v>545041</v>
       </c>
       <c r="R21" t="n">
-        <v>7244443</v>
+        <v>7244311</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3011,11 +3011,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3035,9 +3030,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3058,7 +3058,7 @@
         <v>127727421</v>
       </c>
       <c r="B22" t="n">
-        <v>92029</v>
+        <v>92035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>127727472</v>
       </c>
       <c r="B23" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127727459</v>
       </c>
       <c r="B2" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>127727480</v>
       </c>
       <c r="B3" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>127727425</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727430</v>
+        <v>127727463</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>91359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544978</v>
+        <v>545110</v>
       </c>
       <c r="R5" t="n">
-        <v>7244472</v>
+        <v>7244381</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,11 +1104,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1135,12 +1125,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1158,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727463</v>
+        <v>127727467</v>
       </c>
       <c r="B6" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545110</v>
+        <v>544936</v>
       </c>
       <c r="R6" t="n">
-        <v>7244381</v>
+        <v>7244266</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1252,12 +1242,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt 2-stammig</t>
+          <t>Levande, grov gran</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
+          <t>Picea abies # Levande, grov gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1275,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727467</v>
+        <v>127727430</v>
       </c>
       <c r="B7" t="n">
-        <v>91356</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,34 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544936</v>
+        <v>544978</v>
       </c>
       <c r="R7" t="n">
-        <v>7244266</v>
+        <v>7244472</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,6 +1343,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Levande, grov gran</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Levande, grov gran</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727431</v>
+        <v>127727458</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>91359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,39 +1403,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545054</v>
+        <v>545033</v>
       </c>
       <c r="R8" t="n">
-        <v>7244432</v>
+        <v>7244298</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1470,11 +1465,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1496,12 +1486,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1519,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727458</v>
+        <v>127727431</v>
       </c>
       <c r="B9" t="n">
-        <v>91356</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,34 +1520,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545033</v>
+        <v>545054</v>
       </c>
       <c r="R9" t="n">
-        <v>7244298</v>
+        <v>7244432</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1592,6 +1587,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
         <v>127727454</v>
       </c>
       <c r="B10" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>127727437</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>127727427</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>127727469</v>
       </c>
       <c r="B13" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127727464</v>
       </c>
       <c r="B14" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>127727443</v>
       </c>
       <c r="B15" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>127727423</v>
       </c>
       <c r="B16" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2465,45 +2465,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727442</v>
+        <v>127727426</v>
       </c>
       <c r="B17" t="n">
-        <v>91792</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545031</v>
+        <v>545100</v>
       </c>
       <c r="R17" t="n">
-        <v>7244445</v>
+        <v>7244443</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2538,6 +2543,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2557,14 +2567,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2582,10 +2587,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727426</v>
+        <v>127727451</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>91337</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,39 +2598,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545100</v>
+        <v>545094</v>
       </c>
       <c r="R18" t="n">
-        <v>7244443</v>
+        <v>7244392</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2660,11 +2660,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2684,9 +2679,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2704,32 +2704,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727451</v>
+        <v>127727442</v>
       </c>
       <c r="B19" t="n">
-        <v>91334</v>
+        <v>91795</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545094</v>
+        <v>545031</v>
       </c>
       <c r="R19" t="n">
-        <v>7244392</v>
+        <v>7244445</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2798,12 +2798,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2824,7 +2824,7 @@
         <v>127727474</v>
       </c>
       <c r="B20" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>127727466</v>
       </c>
       <c r="B21" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3055,32 +3055,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727421</v>
+        <v>127727472</v>
       </c>
       <c r="B22" t="n">
-        <v>92035</v>
+        <v>91359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544863</v>
+        <v>544968</v>
       </c>
       <c r="R22" t="n">
-        <v>7244369</v>
+        <v>7244261</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3172,32 +3172,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727472</v>
+        <v>127727421</v>
       </c>
       <c r="B23" t="n">
-        <v>91356</v>
+        <v>92038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544968</v>
+        <v>544863</v>
       </c>
       <c r="R23" t="n">
-        <v>7244261</v>
+        <v>7244369</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3292,7 +3292,7 @@
         <v>127727433</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127727459</v>
       </c>
       <c r="B2" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>127727480</v>
       </c>
       <c r="B3" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>127727425</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>127727463</v>
       </c>
       <c r="B5" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>127727467</v>
       </c>
       <c r="B6" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>127727430</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>127727458</v>
       </c>
       <c r="B8" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127727431</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127727454</v>
       </c>
       <c r="B10" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727437</v>
+        <v>127727427</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545110</v>
+        <v>544900</v>
       </c>
       <c r="R11" t="n">
-        <v>7244346</v>
+        <v>7244331</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack lågt ned</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,14 +1850,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granlåga, ny rotvälta</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, ny rotvälta</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1875,10 +1870,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727427</v>
+        <v>127727437</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,10 +1910,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544900</v>
+        <v>545110</v>
       </c>
       <c r="R12" t="n">
-        <v>7244331</v>
+        <v>7244346</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1955,7 +1950,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack lågt ned</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,9 +1972,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granlåga, ny rotvälta</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, ny rotvälta</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>127727469</v>
       </c>
       <c r="B13" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127727464</v>
       </c>
       <c r="B14" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>127727443</v>
       </c>
       <c r="B15" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>127727423</v>
       </c>
       <c r="B16" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727426</v>
+        <v>127727474</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>91367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,39 +2476,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545100</v>
+        <v>544931</v>
       </c>
       <c r="R17" t="n">
-        <v>7244443</v>
+        <v>7244255</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2543,11 +2538,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2567,9 +2557,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2587,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727451</v>
+        <v>127727466</v>
       </c>
       <c r="B18" t="n">
-        <v>91337</v>
+        <v>91367</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,21 +2593,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2622,10 +2617,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545094</v>
+        <v>545041</v>
       </c>
       <c r="R18" t="n">
-        <v>7244392</v>
+        <v>7244311</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2681,12 +2676,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2704,45 +2699,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727442</v>
+        <v>127727426</v>
       </c>
       <c r="B19" t="n">
-        <v>91795</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545031</v>
+        <v>545100</v>
       </c>
       <c r="R19" t="n">
-        <v>7244445</v>
+        <v>7244443</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2777,6 +2777,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2796,14 +2801,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2821,32 +2821,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127727474</v>
+        <v>127727442</v>
       </c>
       <c r="B20" t="n">
-        <v>91359</v>
+        <v>91803</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544931</v>
+        <v>545031</v>
       </c>
       <c r="R20" t="n">
-        <v>7244255</v>
+        <v>7244445</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2915,12 +2915,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727466</v>
+        <v>127727451</v>
       </c>
       <c r="B21" t="n">
-        <v>91359</v>
+        <v>91345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2949,21 +2949,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545041</v>
+        <v>545094</v>
       </c>
       <c r="R21" t="n">
-        <v>7244311</v>
+        <v>7244392</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3055,32 +3055,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727472</v>
+        <v>127727421</v>
       </c>
       <c r="B22" t="n">
-        <v>91359</v>
+        <v>92046</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544968</v>
+        <v>544863</v>
       </c>
       <c r="R22" t="n">
-        <v>7244261</v>
+        <v>7244369</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3172,32 +3172,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727421</v>
+        <v>127727472</v>
       </c>
       <c r="B23" t="n">
-        <v>92038</v>
+        <v>91367</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544863</v>
+        <v>544968</v>
       </c>
       <c r="R23" t="n">
-        <v>7244369</v>
+        <v>7244261</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3292,7 +3292,7 @@
         <v>127727433</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127727459</v>
       </c>
       <c r="B2" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727480</v>
+        <v>127727425</v>
       </c>
       <c r="B3" t="n">
-        <v>88752</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545088</v>
+        <v>545022</v>
       </c>
       <c r="R3" t="n">
-        <v>7244350</v>
+        <v>7244468</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,6 +870,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -884,14 +894,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Granlåga toppknäckt</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga toppknäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727425</v>
+        <v>127727480</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>88753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545022</v>
+        <v>545088</v>
       </c>
       <c r="R4" t="n">
-        <v>7244468</v>
+        <v>7244350</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,11 +987,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1011,9 +1006,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Granlåga toppknäckt</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga toppknäckt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
         <v>127727463</v>
       </c>
       <c r="B5" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>127727467</v>
       </c>
       <c r="B6" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727458</v>
+        <v>127727431</v>
       </c>
       <c r="B8" t="n">
-        <v>91367</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,34 +1403,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545033</v>
+        <v>545054</v>
       </c>
       <c r="R8" t="n">
-        <v>7244298</v>
+        <v>7244432</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,6 +1470,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1486,12 +1496,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1509,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727431</v>
+        <v>127727458</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,39 +1530,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545054</v>
+        <v>545033</v>
       </c>
       <c r="R9" t="n">
-        <v>7244432</v>
+        <v>7244298</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1587,11 +1592,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
         <v>127727454</v>
       </c>
       <c r="B10" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727427</v>
+        <v>127727437</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544900</v>
+        <v>545110</v>
       </c>
       <c r="R11" t="n">
-        <v>7244331</v>
+        <v>7244346</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack lågt ned</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,9 +1850,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granlåga, ny rotvälta</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, ny rotvälta</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1870,7 +1875,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727437</v>
+        <v>127727427</v>
       </c>
       <c r="B12" t="n">
         <v>57672</v>
@@ -1910,10 +1915,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545110</v>
+        <v>544900</v>
       </c>
       <c r="R12" t="n">
-        <v>7244346</v>
+        <v>7244331</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1950,7 +1955,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack lågt ned</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,14 +1977,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granlåga, ny rotvälta</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, ny rotvälta</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>127727469</v>
       </c>
       <c r="B13" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127727464</v>
       </c>
       <c r="B14" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>127727443</v>
       </c>
       <c r="B15" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>127727423</v>
       </c>
       <c r="B16" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>127727474</v>
       </c>
       <c r="B17" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>127727466</v>
       </c>
       <c r="B18" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727426</v>
+        <v>127727451</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,39 +2710,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545100</v>
+        <v>545094</v>
       </c>
       <c r="R19" t="n">
-        <v>7244443</v>
+        <v>7244392</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2777,11 +2772,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2801,9 +2791,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2824,7 +2819,7 @@
         <v>127727442</v>
       </c>
       <c r="B20" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2938,10 +2933,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727451</v>
+        <v>127727426</v>
       </c>
       <c r="B21" t="n">
-        <v>91345</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2949,34 +2944,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545094</v>
+        <v>545100</v>
       </c>
       <c r="R21" t="n">
-        <v>7244392</v>
+        <v>7244443</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3011,6 +3011,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3030,14 +3035,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3058,7 +3058,7 @@
         <v>127727421</v>
       </c>
       <c r="B22" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>127727472</v>
       </c>
       <c r="B23" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727463</v>
+        <v>127727430</v>
       </c>
       <c r="B5" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545110</v>
+        <v>544978</v>
       </c>
       <c r="R5" t="n">
-        <v>7244381</v>
+        <v>7244472</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,6 +1109,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,12 +1135,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt 2-stammig</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,7 +1158,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727467</v>
+        <v>127727463</v>
       </c>
       <c r="B6" t="n">
         <v>91368</v>
@@ -1183,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544936</v>
+        <v>545110</v>
       </c>
       <c r="R6" t="n">
-        <v>7244266</v>
+        <v>7244381</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,12 +1252,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Levande, grov gran</t>
+          <t>Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Levande, grov gran</t>
+          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727430</v>
+        <v>127727467</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544978</v>
+        <v>544936</v>
       </c>
       <c r="R7" t="n">
-        <v>7244472</v>
+        <v>7244266</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,11 +1348,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Levande, grov gran</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Levande, grov gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727431</v>
+        <v>127727458</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,39 +1403,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545054</v>
+        <v>545033</v>
       </c>
       <c r="R8" t="n">
-        <v>7244432</v>
+        <v>7244298</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1470,11 +1465,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1496,12 +1486,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1519,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727458</v>
+        <v>127727431</v>
       </c>
       <c r="B9" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,34 +1520,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545033</v>
+        <v>545054</v>
       </c>
       <c r="R9" t="n">
-        <v>7244298</v>
+        <v>7244432</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1592,6 +1587,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2465,32 +2465,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727474</v>
+        <v>127727442</v>
       </c>
       <c r="B17" t="n">
-        <v>91368</v>
+        <v>91804</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544931</v>
+        <v>545031</v>
       </c>
       <c r="R17" t="n">
-        <v>7244255</v>
+        <v>7244445</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727466</v>
+        <v>127727451</v>
       </c>
       <c r="B18" t="n">
-        <v>91368</v>
+        <v>91346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,21 +2593,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545041</v>
+        <v>545094</v>
       </c>
       <c r="R18" t="n">
-        <v>7244311</v>
+        <v>7244392</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727451</v>
+        <v>127727474</v>
       </c>
       <c r="B19" t="n">
-        <v>91346</v>
+        <v>91368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545094</v>
+        <v>544931</v>
       </c>
       <c r="R19" t="n">
-        <v>7244392</v>
+        <v>7244255</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2816,32 +2816,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127727442</v>
+        <v>127727466</v>
       </c>
       <c r="B20" t="n">
-        <v>91804</v>
+        <v>91368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545031</v>
+        <v>545041</v>
       </c>
       <c r="R20" t="n">
-        <v>7244445</v>
+        <v>7244311</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127727459</v>
       </c>
       <c r="B2" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>127727480</v>
       </c>
       <c r="B4" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727430</v>
+        <v>127727463</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544978</v>
+        <v>545110</v>
       </c>
       <c r="R5" t="n">
-        <v>7244472</v>
+        <v>7244381</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,11 +1104,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1135,12 +1125,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1158,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727463</v>
+        <v>127727467</v>
       </c>
       <c r="B6" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545110</v>
+        <v>544936</v>
       </c>
       <c r="R6" t="n">
-        <v>7244381</v>
+        <v>7244266</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1252,12 +1242,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt 2-stammig</t>
+          <t>Levande, grov gran</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
+          <t>Picea abies # Levande, grov gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1275,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727467</v>
+        <v>127727430</v>
       </c>
       <c r="B7" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,34 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544936</v>
+        <v>544978</v>
       </c>
       <c r="R7" t="n">
-        <v>7244266</v>
+        <v>7244472</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,6 +1343,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Levande, grov gran</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Levande, grov gran</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
         <v>127727458</v>
       </c>
       <c r="B8" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127727454</v>
       </c>
       <c r="B10" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>127727469</v>
       </c>
       <c r="B13" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127727464</v>
       </c>
       <c r="B14" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>127727443</v>
       </c>
       <c r="B15" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>127727423</v>
       </c>
       <c r="B16" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2465,32 +2465,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727442</v>
+        <v>127727451</v>
       </c>
       <c r="B17" t="n">
-        <v>91804</v>
+        <v>91347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545031</v>
+        <v>545094</v>
       </c>
       <c r="R17" t="n">
-        <v>7244445</v>
+        <v>7244392</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2582,32 +2582,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727451</v>
+        <v>127727442</v>
       </c>
       <c r="B18" t="n">
-        <v>91346</v>
+        <v>91805</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545094</v>
+        <v>545031</v>
       </c>
       <c r="R18" t="n">
-        <v>7244392</v>
+        <v>7244445</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2702,7 +2702,7 @@
         <v>127727474</v>
       </c>
       <c r="B19" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>127727466</v>
       </c>
       <c r="B20" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>127727421</v>
       </c>
       <c r="B22" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3172,10 +3172,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727472</v>
+        <v>127727433</v>
       </c>
       <c r="B23" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,34 +3183,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544968</v>
+        <v>545069</v>
       </c>
       <c r="R23" t="n">
-        <v>7244261</v>
+        <v>7244335</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3245,6 +3250,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3264,14 +3274,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3289,10 +3294,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727433</v>
+        <v>127727472</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3300,39 +3305,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545069</v>
+        <v>544968</v>
       </c>
       <c r="R24" t="n">
-        <v>7244335</v>
+        <v>7244261</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3367,11 +3367,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3391,9 +3386,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127727459</v>
       </c>
       <c r="B2" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727425</v>
+        <v>127727480</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>88755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545022</v>
+        <v>545088</v>
       </c>
       <c r="R3" t="n">
-        <v>7244468</v>
+        <v>7244350</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,11 +865,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -894,9 +884,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granlåga toppknäckt</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga toppknäckt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727480</v>
+        <v>127727425</v>
       </c>
       <c r="B4" t="n">
-        <v>88754</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545088</v>
+        <v>545022</v>
       </c>
       <c r="R4" t="n">
-        <v>7244350</v>
+        <v>7244468</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,6 +987,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1006,14 +1011,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Granlåga toppknäckt</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga toppknäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
         <v>127727463</v>
       </c>
       <c r="B5" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>127727467</v>
       </c>
       <c r="B6" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>127727458</v>
       </c>
       <c r="B8" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127727454</v>
       </c>
       <c r="B10" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727437</v>
+        <v>127727427</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545110</v>
+        <v>544900</v>
       </c>
       <c r="R11" t="n">
-        <v>7244346</v>
+        <v>7244331</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack lågt ned</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,14 +1850,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granlåga, ny rotvälta</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, ny rotvälta</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1875,7 +1870,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727427</v>
+        <v>127727437</v>
       </c>
       <c r="B12" t="n">
         <v>57672</v>
@@ -1915,10 +1910,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544900</v>
+        <v>545110</v>
       </c>
       <c r="R12" t="n">
-        <v>7244331</v>
+        <v>7244346</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1955,7 +1950,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack lågt ned</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,9 +1972,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granlåga, ny rotvälta</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, ny rotvälta</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>127727469</v>
       </c>
       <c r="B13" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127727464</v>
       </c>
       <c r="B14" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>127727443</v>
       </c>
       <c r="B15" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>127727423</v>
       </c>
       <c r="B16" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727451</v>
+        <v>127727426</v>
       </c>
       <c r="B17" t="n">
-        <v>91347</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,34 +2476,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545094</v>
+        <v>545100</v>
       </c>
       <c r="R17" t="n">
-        <v>7244392</v>
+        <v>7244443</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2538,6 +2543,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2557,14 +2567,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2582,32 +2587,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727442</v>
+        <v>127727451</v>
       </c>
       <c r="B18" t="n">
-        <v>91805</v>
+        <v>91348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2617,10 +2622,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545031</v>
+        <v>545094</v>
       </c>
       <c r="R18" t="n">
-        <v>7244445</v>
+        <v>7244392</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2676,12 +2681,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2699,32 +2704,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727474</v>
+        <v>127727442</v>
       </c>
       <c r="B19" t="n">
-        <v>91369</v>
+        <v>91806</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2734,10 +2739,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544931</v>
+        <v>545031</v>
       </c>
       <c r="R19" t="n">
-        <v>7244255</v>
+        <v>7244445</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2793,12 +2798,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2816,10 +2821,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127727466</v>
+        <v>127727474</v>
       </c>
       <c r="B20" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,10 +2856,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545041</v>
+        <v>544931</v>
       </c>
       <c r="R20" t="n">
-        <v>7244311</v>
+        <v>7244255</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2910,12 +2915,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2933,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727426</v>
+        <v>127727466</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2944,39 +2949,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545100</v>
+        <v>545041</v>
       </c>
       <c r="R21" t="n">
-        <v>7244443</v>
+        <v>7244311</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3011,11 +3011,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3035,9 +3030,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3055,32 +3055,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727421</v>
+        <v>127727472</v>
       </c>
       <c r="B22" t="n">
-        <v>92048</v>
+        <v>91370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544863</v>
+        <v>544968</v>
       </c>
       <c r="R22" t="n">
-        <v>7244369</v>
+        <v>7244261</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3172,50 +3172,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727433</v>
+        <v>127727421</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>92049</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545069</v>
+        <v>544863</v>
       </c>
       <c r="R23" t="n">
-        <v>7244335</v>
+        <v>7244369</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3250,11 +3245,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3274,9 +3264,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3294,10 +3289,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727472</v>
+        <v>127727433</v>
       </c>
       <c r="B24" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3305,34 +3300,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544968</v>
+        <v>545069</v>
       </c>
       <c r="R24" t="n">
-        <v>7244261</v>
+        <v>7244335</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3367,6 +3367,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3386,14 +3391,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727463</v>
+        <v>127727430</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545110</v>
+        <v>544978</v>
       </c>
       <c r="R5" t="n">
-        <v>7244381</v>
+        <v>7244472</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,6 +1109,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,12 +1135,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt 2-stammig</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,7 +1158,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727467</v>
+        <v>127727463</v>
       </c>
       <c r="B6" t="n">
         <v>91370</v>
@@ -1183,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544936</v>
+        <v>545110</v>
       </c>
       <c r="R6" t="n">
-        <v>7244266</v>
+        <v>7244381</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,12 +1252,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Levande, grov gran</t>
+          <t>Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Levande, grov gran</t>
+          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727430</v>
+        <v>127727467</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544978</v>
+        <v>544936</v>
       </c>
       <c r="R7" t="n">
-        <v>7244472</v>
+        <v>7244266</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,11 +1348,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Levande, grov gran</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Levande, grov gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727427</v>
+        <v>127727437</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544900</v>
+        <v>545110</v>
       </c>
       <c r="R11" t="n">
-        <v>7244331</v>
+        <v>7244346</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack lågt ned</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,9 +1850,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granlåga, ny rotvälta</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, ny rotvälta</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1870,7 +1875,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727437</v>
+        <v>127727427</v>
       </c>
       <c r="B12" t="n">
         <v>57672</v>
@@ -1910,10 +1915,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545110</v>
+        <v>544900</v>
       </c>
       <c r="R12" t="n">
-        <v>7244346</v>
+        <v>7244331</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1950,7 +1955,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack lågt ned</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,14 +1977,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granlåga, ny rotvälta</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, ny rotvälta</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727426</v>
+        <v>127727474</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,39 +2476,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545100</v>
+        <v>544931</v>
       </c>
       <c r="R17" t="n">
-        <v>7244443</v>
+        <v>7244255</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2543,11 +2538,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2567,9 +2557,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2587,10 +2582,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727451</v>
+        <v>127727466</v>
       </c>
       <c r="B18" t="n">
-        <v>91348</v>
+        <v>91370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,21 +2593,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2622,10 +2617,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545094</v>
+        <v>545041</v>
       </c>
       <c r="R18" t="n">
-        <v>7244392</v>
+        <v>7244311</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2681,12 +2676,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2704,45 +2699,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727442</v>
+        <v>127727426</v>
       </c>
       <c r="B19" t="n">
-        <v>91806</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545031</v>
+        <v>545100</v>
       </c>
       <c r="R19" t="n">
-        <v>7244445</v>
+        <v>7244443</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2777,6 +2777,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2796,14 +2801,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127727474</v>
+        <v>127727451</v>
       </c>
       <c r="B20" t="n">
-        <v>91370</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2832,21 +2832,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544931</v>
+        <v>545094</v>
       </c>
       <c r="R20" t="n">
-        <v>7244255</v>
+        <v>7244392</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2915,12 +2915,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2938,32 +2938,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727466</v>
+        <v>127727442</v>
       </c>
       <c r="B21" t="n">
-        <v>91370</v>
+        <v>91806</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545041</v>
+        <v>545031</v>
       </c>
       <c r="R21" t="n">
-        <v>7244311</v>
+        <v>7244445</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3055,32 +3055,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727472</v>
+        <v>127727421</v>
       </c>
       <c r="B22" t="n">
-        <v>91370</v>
+        <v>92049</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544968</v>
+        <v>544863</v>
       </c>
       <c r="R22" t="n">
-        <v>7244261</v>
+        <v>7244369</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3172,32 +3172,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727421</v>
+        <v>127727472</v>
       </c>
       <c r="B23" t="n">
-        <v>92049</v>
+        <v>91370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544863</v>
+        <v>544968</v>
       </c>
       <c r="R23" t="n">
-        <v>7244369</v>
+        <v>7244261</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727430</v>
+        <v>127727463</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544978</v>
+        <v>545110</v>
       </c>
       <c r="R5" t="n">
-        <v>7244472</v>
+        <v>7244381</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,11 +1104,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1135,12 +1125,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1158,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727463</v>
+        <v>127727467</v>
       </c>
       <c r="B6" t="n">
         <v>91370</v>
@@ -1193,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545110</v>
+        <v>544936</v>
       </c>
       <c r="R6" t="n">
-        <v>7244381</v>
+        <v>7244266</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1252,12 +1242,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt 2-stammig</t>
+          <t>Levande, grov gran</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
+          <t>Picea abies # Levande, grov gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1275,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727467</v>
+        <v>127727430</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,34 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544936</v>
+        <v>544978</v>
       </c>
       <c r="R7" t="n">
-        <v>7244266</v>
+        <v>7244472</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,6 +1343,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Levande, grov gran</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Levande, grov gran</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727463</v>
+        <v>127727430</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545110</v>
+        <v>544978</v>
       </c>
       <c r="R5" t="n">
-        <v>7244381</v>
+        <v>7244472</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,6 +1109,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,12 +1135,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt 2-stammig</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,7 +1158,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727467</v>
+        <v>127727463</v>
       </c>
       <c r="B6" t="n">
         <v>91370</v>
@@ -1183,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544936</v>
+        <v>545110</v>
       </c>
       <c r="R6" t="n">
-        <v>7244266</v>
+        <v>7244381</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,12 +1252,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Levande, grov gran</t>
+          <t>Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Levande, grov gran</t>
+          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727430</v>
+        <v>127727467</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544978</v>
+        <v>544936</v>
       </c>
       <c r="R7" t="n">
-        <v>7244472</v>
+        <v>7244266</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,11 +1348,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Levande, grov gran</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Levande, grov gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727472</v>
+        <v>127727433</v>
       </c>
       <c r="B23" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,34 +3183,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544968</v>
+        <v>545069</v>
       </c>
       <c r="R23" t="n">
-        <v>7244261</v>
+        <v>7244335</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3245,6 +3250,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3264,14 +3274,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3289,10 +3294,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727433</v>
+        <v>127727472</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3300,39 +3305,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545069</v>
+        <v>544968</v>
       </c>
       <c r="R24" t="n">
-        <v>7244335</v>
+        <v>7244261</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3367,11 +3367,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3391,9 +3386,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727463</v>
+        <v>127727430</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545110</v>
+        <v>544978</v>
       </c>
       <c r="R5" t="n">
-        <v>7244381</v>
+        <v>7244472</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,6 +1109,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,12 +1135,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt 2-stammig</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,7 +1158,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727467</v>
+        <v>127727463</v>
       </c>
       <c r="B6" t="n">
         <v>91370</v>
@@ -1183,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544936</v>
+        <v>545110</v>
       </c>
       <c r="R6" t="n">
-        <v>7244266</v>
+        <v>7244381</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,12 +1252,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Levande, grov gran</t>
+          <t>Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Levande, grov gran</t>
+          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727430</v>
+        <v>127727467</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544978</v>
+        <v>544936</v>
       </c>
       <c r="R7" t="n">
-        <v>7244472</v>
+        <v>7244266</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,11 +1348,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Levande, grov gran</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Levande, grov gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -3172,10 +3172,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727433</v>
+        <v>127727472</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,39 +3183,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545069</v>
+        <v>544968</v>
       </c>
       <c r="R23" t="n">
-        <v>7244335</v>
+        <v>7244261</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3250,11 +3245,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3274,9 +3264,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3294,10 +3289,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727472</v>
+        <v>127727433</v>
       </c>
       <c r="B24" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3305,34 +3300,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544968</v>
+        <v>545069</v>
       </c>
       <c r="R24" t="n">
-        <v>7244261</v>
+        <v>7244335</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3367,6 +3367,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3386,14 +3391,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727430</v>
+        <v>127727463</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544978</v>
+        <v>545110</v>
       </c>
       <c r="R5" t="n">
-        <v>7244472</v>
+        <v>7244381</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,11 +1104,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1135,12 +1125,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1158,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727463</v>
+        <v>127727467</v>
       </c>
       <c r="B6" t="n">
         <v>91370</v>
@@ -1193,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545110</v>
+        <v>544936</v>
       </c>
       <c r="R6" t="n">
-        <v>7244381</v>
+        <v>7244266</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1252,12 +1242,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt 2-stammig</t>
+          <t>Levande, grov gran</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
+          <t>Picea abies # Levande, grov gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1275,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727467</v>
+        <v>127727430</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,34 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544936</v>
+        <v>544978</v>
       </c>
       <c r="R7" t="n">
-        <v>7244266</v>
+        <v>7244472</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,6 +1343,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Levande, grov gran</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Levande, grov gran</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727472</v>
+        <v>127727433</v>
       </c>
       <c r="B23" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,34 +3183,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544968</v>
+        <v>545069</v>
       </c>
       <c r="R23" t="n">
-        <v>7244261</v>
+        <v>7244335</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3245,6 +3250,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3264,14 +3274,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3289,10 +3294,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727433</v>
+        <v>127727472</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3300,39 +3305,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545069</v>
+        <v>544968</v>
       </c>
       <c r="R24" t="n">
-        <v>7244335</v>
+        <v>7244261</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3367,11 +3367,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3391,9 +3386,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127727459</v>
       </c>
       <c r="B2" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727480</v>
+        <v>127727425</v>
       </c>
       <c r="B3" t="n">
-        <v>88755</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545088</v>
+        <v>545022</v>
       </c>
       <c r="R3" t="n">
-        <v>7244350</v>
+        <v>7244468</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,6 +870,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -884,14 +894,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Granlåga toppknäckt</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga toppknäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727425</v>
+        <v>127727480</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>88761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545022</v>
+        <v>545088</v>
       </c>
       <c r="R4" t="n">
-        <v>7244468</v>
+        <v>7244350</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,11 +987,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1011,9 +1006,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Granlåga toppknäckt</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga toppknäckt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727463</v>
+        <v>127727430</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545110</v>
+        <v>544978</v>
       </c>
       <c r="R5" t="n">
-        <v>7244381</v>
+        <v>7244472</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,6 +1109,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,12 +1135,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt 2-stammig</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727467</v>
+        <v>127727463</v>
       </c>
       <c r="B6" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544936</v>
+        <v>545110</v>
       </c>
       <c r="R6" t="n">
-        <v>7244266</v>
+        <v>7244381</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,12 +1252,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Levande, grov gran</t>
+          <t>Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Levande, grov gran</t>
+          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727430</v>
+        <v>127727467</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>91378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544978</v>
+        <v>544936</v>
       </c>
       <c r="R7" t="n">
-        <v>7244472</v>
+        <v>7244266</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,11 +1348,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Levande, grov gran</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Levande, grov gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
         <v>127727458</v>
       </c>
       <c r="B8" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127727431</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127727454</v>
       </c>
       <c r="B10" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727437</v>
+        <v>127727427</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545110</v>
+        <v>544900</v>
       </c>
       <c r="R11" t="n">
-        <v>7244346</v>
+        <v>7244331</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack lågt ned</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,14 +1850,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granlåga, ny rotvälta</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, ny rotvälta</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1875,10 +1870,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727427</v>
+        <v>127727437</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,10 +1910,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544900</v>
+        <v>545110</v>
       </c>
       <c r="R12" t="n">
-        <v>7244331</v>
+        <v>7244346</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1955,7 +1950,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack lågt ned</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,9 +1972,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granlåga, ny rotvälta</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, ny rotvälta</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>127727469</v>
       </c>
       <c r="B13" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127727464</v>
       </c>
       <c r="B14" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>127727443</v>
       </c>
       <c r="B15" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>127727423</v>
       </c>
       <c r="B16" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>127727474</v>
       </c>
       <c r="B17" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>127727466</v>
       </c>
       <c r="B18" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727426</v>
+        <v>127727451</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,39 +2710,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545100</v>
+        <v>545094</v>
       </c>
       <c r="R19" t="n">
-        <v>7244443</v>
+        <v>7244392</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2777,11 +2772,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2801,9 +2791,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2821,32 +2816,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127727451</v>
+        <v>127727442</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>91814</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2856,10 +2851,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545094</v>
+        <v>545031</v>
       </c>
       <c r="R20" t="n">
-        <v>7244392</v>
+        <v>7244445</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2915,12 +2910,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2938,45 +2933,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727442</v>
+        <v>127727426</v>
       </c>
       <c r="B21" t="n">
-        <v>91806</v>
+        <v>57673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545031</v>
+        <v>545100</v>
       </c>
       <c r="R21" t="n">
-        <v>7244445</v>
+        <v>7244443</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3011,6 +3011,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3030,14 +3035,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3055,32 +3055,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127727421</v>
+        <v>127727472</v>
       </c>
       <c r="B22" t="n">
-        <v>92049</v>
+        <v>91378</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544863</v>
+        <v>544968</v>
       </c>
       <c r="R22" t="n">
-        <v>7244369</v>
+        <v>7244261</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3175,7 +3175,7 @@
         <v>127727433</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727472</v>
+        <v>127727421</v>
       </c>
       <c r="B24" t="n">
-        <v>91370</v>
+        <v>92057</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544968</v>
+        <v>544863</v>
       </c>
       <c r="R24" t="n">
-        <v>7244261</v>
+        <v>7244369</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727425</v>
+        <v>127727480</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>88761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545022</v>
+        <v>545088</v>
       </c>
       <c r="R3" t="n">
-        <v>7244468</v>
+        <v>7244350</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,11 +865,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -894,9 +884,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granlåga toppknäckt</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga toppknäckt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727480</v>
+        <v>127727425</v>
       </c>
       <c r="B4" t="n">
-        <v>88761</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545088</v>
+        <v>545022</v>
       </c>
       <c r="R4" t="n">
-        <v>7244350</v>
+        <v>7244468</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,6 +987,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1006,14 +1011,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Granlåga toppknäckt</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga toppknäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727430</v>
+        <v>127727463</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>91378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544978</v>
+        <v>545110</v>
       </c>
       <c r="R5" t="n">
-        <v>7244472</v>
+        <v>7244381</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,11 +1104,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1135,12 +1125,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1158,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727463</v>
+        <v>127727467</v>
       </c>
       <c r="B6" t="n">
         <v>91378</v>
@@ -1193,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545110</v>
+        <v>544936</v>
       </c>
       <c r="R6" t="n">
-        <v>7244381</v>
+        <v>7244266</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1252,12 +1242,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt 2-stammig</t>
+          <t>Levande, grov gran</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
+          <t>Picea abies # Levande, grov gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1275,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727467</v>
+        <v>127727430</v>
       </c>
       <c r="B7" t="n">
-        <v>91378</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,34 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544936</v>
+        <v>544978</v>
       </c>
       <c r="R7" t="n">
-        <v>7244266</v>
+        <v>7244472</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,6 +1343,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Levande, grov gran</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Levande, grov gran</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127727459</v>
       </c>
       <c r="B2" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727480</v>
+        <v>127727425</v>
       </c>
       <c r="B3" t="n">
-        <v>88761</v>
+        <v>57684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545088</v>
+        <v>545022</v>
       </c>
       <c r="R3" t="n">
-        <v>7244350</v>
+        <v>7244468</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,6 +870,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -884,14 +894,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Granlåga toppknäckt</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga toppknäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727425</v>
+        <v>127727480</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>88772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545022</v>
+        <v>545088</v>
       </c>
       <c r="R4" t="n">
-        <v>7244468</v>
+        <v>7244350</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,11 +987,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1011,9 +1006,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Granlåga toppknäckt</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga toppknäckt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
         <v>127727463</v>
       </c>
       <c r="B5" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>127727467</v>
       </c>
       <c r="B6" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>127727430</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>127727458</v>
       </c>
       <c r="B8" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127727431</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127727454</v>
       </c>
       <c r="B10" t="n">
-        <v>91356</v>
+        <v>91367</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727427</v>
+        <v>127727437</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544900</v>
+        <v>545110</v>
       </c>
       <c r="R11" t="n">
-        <v>7244331</v>
+        <v>7244346</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack lågt ned</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,9 +1850,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granlåga, ny rotvälta</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, ny rotvälta</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1870,10 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727437</v>
+        <v>127727427</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,10 +1915,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545110</v>
+        <v>544900</v>
       </c>
       <c r="R12" t="n">
-        <v>7244346</v>
+        <v>7244331</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1950,7 +1955,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack lågt ned</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,14 +1977,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granlåga, ny rotvälta</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, ny rotvälta</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>127727469</v>
       </c>
       <c r="B13" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>127727464</v>
       </c>
       <c r="B14" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>127727443</v>
       </c>
       <c r="B15" t="n">
-        <v>91656</v>
+        <v>91667</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>127727423</v>
       </c>
       <c r="B16" t="n">
-        <v>92057</v>
+        <v>92068</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727474</v>
+        <v>127727426</v>
       </c>
       <c r="B17" t="n">
-        <v>91378</v>
+        <v>57684</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,34 +2476,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544931</v>
+        <v>545100</v>
       </c>
       <c r="R17" t="n">
-        <v>7244255</v>
+        <v>7244443</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2538,6 +2543,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2557,14 +2567,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2582,10 +2587,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127727466</v>
+        <v>127727451</v>
       </c>
       <c r="B18" t="n">
-        <v>91378</v>
+        <v>91367</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,21 +2598,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2617,10 +2622,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545041</v>
+        <v>545094</v>
       </c>
       <c r="R18" t="n">
-        <v>7244311</v>
+        <v>7244392</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2676,12 +2681,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2699,32 +2704,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127727451</v>
+        <v>127727442</v>
       </c>
       <c r="B19" t="n">
-        <v>91356</v>
+        <v>91825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2734,10 +2739,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545094</v>
+        <v>545031</v>
       </c>
       <c r="R19" t="n">
-        <v>7244392</v>
+        <v>7244445</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2793,12 +2798,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Granstubbe</t>
+          <t>Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2816,32 +2821,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127727442</v>
+        <v>127727466</v>
       </c>
       <c r="B20" t="n">
-        <v>91814</v>
+        <v>91389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,10 +2856,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545031</v>
+        <v>545041</v>
       </c>
       <c r="R20" t="n">
-        <v>7244445</v>
+        <v>7244311</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2910,12 +2915,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2933,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127727426</v>
+        <v>127727474</v>
       </c>
       <c r="B21" t="n">
-        <v>57673</v>
+        <v>91389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2944,39 +2949,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545100</v>
+        <v>544931</v>
       </c>
       <c r="R21" t="n">
-        <v>7244443</v>
+        <v>7244255</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3011,11 +3011,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3035,9 +3030,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3058,7 +3058,7 @@
         <v>127727472</v>
       </c>
       <c r="B22" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3172,50 +3172,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127727433</v>
+        <v>127727421</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>92068</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545069</v>
+        <v>544863</v>
       </c>
       <c r="R23" t="n">
-        <v>7244335</v>
+        <v>7244369</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3250,11 +3245,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3274,9 +3264,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3294,45 +3289,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127727421</v>
+        <v>127727433</v>
       </c>
       <c r="B24" t="n">
-        <v>92057</v>
+        <v>57684</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544863</v>
+        <v>545069</v>
       </c>
       <c r="R24" t="n">
-        <v>7244369</v>
+        <v>7244335</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3367,6 +3367,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3386,14 +3391,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 18873-2025 artfynd.xlsx
+++ b/artfynd/A 18873-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127727459</v>
+        <v>127727480</v>
       </c>
       <c r="B2" t="n">
-        <v>91389</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545133</v>
+        <v>545088</v>
       </c>
       <c r="R2" t="n">
-        <v>7244385</v>
+        <v>7244350</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -769,12 +769,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Granhögstubbe toppknäckt</t>
+          <t>Granlåga toppknäckt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe toppknäckt</t>
+          <t>Picea abies # Granlåga toppknäckt</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127727425</v>
+        <v>127727443</v>
       </c>
       <c r="B3" t="n">
-        <v>57684</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545022</v>
+        <v>545031</v>
       </c>
       <c r="R3" t="n">
-        <v>7244468</v>
+        <v>7244445</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,11 +865,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -894,9 +884,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127727480</v>
+        <v>127727451</v>
       </c>
       <c r="B4" t="n">
-        <v>88772</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545088</v>
+        <v>545094</v>
       </c>
       <c r="R4" t="n">
-        <v>7244350</v>
+        <v>7244392</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,12 +1003,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Granlåga toppknäckt</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga toppknäckt</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127727463</v>
+        <v>127727454</v>
       </c>
       <c r="B5" t="n">
-        <v>91389</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545110</v>
+        <v>544960</v>
       </c>
       <c r="R5" t="n">
-        <v>7244381</v>
+        <v>7244254</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,14 +1118,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt 2-stammig</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt 2-stammig</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127727467</v>
+        <v>127727442</v>
       </c>
       <c r="B6" t="n">
-        <v>91389</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544936</v>
+        <v>545031</v>
       </c>
       <c r="R6" t="n">
-        <v>7244266</v>
+        <v>7244445</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,12 +1232,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Levande, grov gran</t>
+          <t>Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Levande, grov gran</t>
+          <t>Picea abies # Granlåga mossbevuxen</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,50 +1255,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127727430</v>
+        <v>127727421</v>
       </c>
       <c r="B7" t="n">
-        <v>57684</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544978</v>
+        <v>544863</v>
       </c>
       <c r="R7" t="n">
-        <v>7244472</v>
+        <v>7244369</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,11 +1328,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,12 +1349,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1392,32 +1372,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127727458</v>
+        <v>127727423</v>
       </c>
       <c r="B8" t="n">
-        <v>91389</v>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545033</v>
+        <v>544860</v>
       </c>
       <c r="R8" t="n">
-        <v>7244298</v>
+        <v>7244311</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1486,12 +1466,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1509,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127727431</v>
+        <v>127727425</v>
       </c>
       <c r="B9" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545054</v>
+        <v>545022</v>
       </c>
       <c r="R9" t="n">
-        <v>7244432</v>
+        <v>7244468</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1589,7 +1569,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack även högt upp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,14 +1591,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1636,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127727454</v>
+        <v>127727426</v>
       </c>
       <c r="B10" t="n">
-        <v>91367</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,34 +1622,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544960</v>
+        <v>545100</v>
       </c>
       <c r="R10" t="n">
-        <v>7244254</v>
+        <v>7244443</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1707,6 +1687,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack även högt upp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127727437</v>
+        <v>127727427</v>
       </c>
       <c r="B11" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545110</v>
+        <v>544900</v>
       </c>
       <c r="R11" t="n">
-        <v>7244346</v>
+        <v>7244331</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,7 +1813,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack lågt ned</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,14 +1835,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granlåga, ny rotvälta</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, ny rotvälta</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1875,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127727427</v>
+        <v>127727430</v>
       </c>
       <c r="B12" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544900</v>
+        <v>544978</v>
       </c>
       <c r="R12" t="n">
-        <v>7244331</v>
+        <v>7244472</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1955,7 +1935,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack lågt ned</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,9 +1957,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1997,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127727469</v>
+        <v>127727431</v>
       </c>
       <c r="B13" t="n">
-        <v>91389</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,31 +1993,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544954</v>
+        <v>545054</v>
       </c>
       <c r="R13" t="n">
         <v>7244432</v>
@@ -2068,6 +2058,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2114,10 +2109,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127727464</v>
+        <v>127727433</v>
       </c>
       <c r="B14" t="n">
-        <v>91389</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,34 +2120,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545131</v>
+        <v>545069</v>
       </c>
       <c r="R14" t="n">
-        <v>7244423</v>
+        <v>7244335</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2187,6 +2187,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2206,14 +2211,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127727443</v>
+        <v>127727437</v>
       </c>
       <c r="B15" t="n">
-        <v>91667</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,34 +2242,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545031</v>
+        <v>545110</v>
       </c>
       <c r="R15" t="n">
-        <v>7244445</v>
+        <v>7244346</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2304,6 +2309,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2325,12 +2335,12 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Granlåga mossbevuxen</t>
+          <t>Granlåga, ny rotvälta</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies # Granlåga, ny rotvälta</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2348,45 +2358,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127727423</v>
+        <v>127727438</v>
       </c>
       <c r="B16" t="n">
-        <v>92068</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skansnäsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544860</v>
+        <v>544922</v>
       </c>
       <c r="R16" t="n">
-        <v>7244311</v>
+        <v>7244247</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2421,6 +2436,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2440,14 +2460,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2465,27 +2480,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127727426</v>
+        <v>127727449</v>
       </c>
       <c r="B17" t="n">
-        <v>57684</v>
+        <v>58327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2496,7 +2511,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2505,10 +2520,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545100</v>
+        <v>544923</v>
       </c>
       <c r="R17" t="n">
-        <v>7244443</v>
+        <v>7244246</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2543,11 +2558,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack även högt upp</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2556,21 +2566,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2584,830 +2579,6 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>127727451</v>
-      </c>
-      <c r="B18" t="n">
-        <v>91367</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Skansnäsliden, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>545094</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7244392</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>127727442</v>
-      </c>
-      <c r="B19" t="n">
-        <v>91825</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Skansnäsliden, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>545031</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7244445</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>127727466</v>
-      </c>
-      <c r="B20" t="n">
-        <v>91389</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Skansnäsliden, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>545041</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7244311</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>127727474</v>
-      </c>
-      <c r="B21" t="n">
-        <v>91389</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Skansnäsliden, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>544931</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7244255</v>
-      </c>
-      <c r="S21" t="n">
-        <v>5</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>127727472</v>
-      </c>
-      <c r="B22" t="n">
-        <v>91389</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Skansnäsliden, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>544968</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7244261</v>
-      </c>
-      <c r="S22" t="n">
-        <v>5</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>127727421</v>
-      </c>
-      <c r="B23" t="n">
-        <v>92068</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Skansnäsliden, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>544863</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7244369</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>127727433</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57684</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Skansnäsliden, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>545069</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7244335</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Via Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
